--- a/JAM01N.xlsx
+++ b/JAM01N.xlsx
@@ -11,27 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="77">
   <si>
     <t/>
   </si>
   <si>
+    <t>10036688</t>
+  </si>
+  <si>
+    <t>CERES RICE CLASS 140</t>
+  </si>
+  <si>
+    <t>JAM01N</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
     <t>10000129</t>
   </si>
   <si>
     <t>CERES RICE FESTIVE80</t>
   </si>
   <si>
-    <t>JAM01N</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
   </si>
   <si>
     <t>10000128</t>
@@ -628,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -672,18 +678,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -692,18 +698,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -712,50 +718,50 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -769,13 +775,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -789,13 +795,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -809,13 +815,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -829,13 +835,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -849,13 +855,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,53 +895,53 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,13 +975,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,53 +995,53 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1049,13 +1055,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1069,13 +1075,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,13 +1095,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,13 +1115,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1129,13 +1135,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,13 +1155,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1169,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,13 +1195,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,13 +1215,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,13 +1235,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,13 +1255,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,13 +1275,33 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/JAM01N.xlsx
+++ b/JAM01N.xlsx
@@ -1261,7 +1261,7 @@
         <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">

--- a/JAM01N.xlsx
+++ b/JAM01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="75">
   <si>
     <t/>
   </si>
@@ -212,12 +212,6 @@
   </si>
   <si>
     <t>CERES DBL HZLNUT 350</t>
-  </si>
-  <si>
-    <t>20109980</t>
-  </si>
-  <si>
-    <t>OVOMALTINE BTL 230G</t>
   </si>
   <si>
     <t>20053052</t>
@@ -634,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1218,10 +1212,10 @@
         <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1238,10 +1232,10 @@
         <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1258,10 +1252,10 @@
         <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1278,29 +1272,9 @@
         <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F33" s="1" t="s">
         <v>38</v>
       </c>
     </row>

--- a/JAM01N.xlsx
+++ b/JAM01N.xlsx
@@ -154,58 +154,58 @@
     <t>BELLA SPRD CHO.CS300</t>
   </si>
   <si>
+    <t>20139437</t>
+  </si>
+  <si>
+    <t>DLMONTE PNUT BTR 170</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>20139437</t>
-  </si>
-  <si>
-    <t>DLMONTE PNUT BTR 170</t>
+    <t>10004771</t>
+  </si>
+  <si>
+    <t>CERES MILK HAZEL.350</t>
+  </si>
+  <si>
+    <t>20096796</t>
+  </si>
+  <si>
+    <t>IDM SPREAD CHOC 150</t>
+  </si>
+  <si>
+    <t>20096794</t>
+  </si>
+  <si>
+    <t>IDM JAM PINEAPPLE170</t>
+  </si>
+  <si>
+    <t>20096795</t>
+  </si>
+  <si>
+    <t>IDM JAM STRAW 170</t>
+  </si>
+  <si>
+    <t>20070629</t>
+  </si>
+  <si>
+    <t>SKIPPY CREAMY 170G</t>
+  </si>
+  <si>
+    <t>20122031</t>
+  </si>
+  <si>
+    <t>SKIPPY CHUNKY 170G</t>
+  </si>
+  <si>
+    <t>20139438</t>
+  </si>
+  <si>
+    <t>DLMONTE CHO HZL 190G</t>
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>10004771</t>
-  </si>
-  <si>
-    <t>CERES MILK HAZEL.350</t>
-  </si>
-  <si>
-    <t>20096796</t>
-  </si>
-  <si>
-    <t>IDM SPREAD CHOC 150</t>
-  </si>
-  <si>
-    <t>20096794</t>
-  </si>
-  <si>
-    <t>IDM JAM PINEAPPLE170</t>
-  </si>
-  <si>
-    <t>20096795</t>
-  </si>
-  <si>
-    <t>IDM JAM STRAW 170</t>
-  </si>
-  <si>
-    <t>20070629</t>
-  </si>
-  <si>
-    <t>SKIPPY CREAMY 170G</t>
-  </si>
-  <si>
-    <t>20122031</t>
-  </si>
-  <si>
-    <t>SKIPPY CHUNKY 170G</t>
-  </si>
-  <si>
-    <t>20139438</t>
-  </si>
-  <si>
-    <t>DLMONTE CHO HZL 190G</t>
   </si>
   <si>
     <t>20041422</t>
@@ -952,7 +952,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>38</v>
@@ -972,7 +972,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>38</v>
@@ -992,7 +992,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -1012,7 +1012,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>15</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1032,7 +1032,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>15</v>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1060,10 +1060,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1152,7 +1152,7 @@
         <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1172,7 +1172,7 @@
         <v>35</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>15</v>
@@ -1189,7 +1189,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>4</v>
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
@@ -1229,7 +1229,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>11</v>
@@ -1249,7 +1249,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>14</v>
@@ -1269,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>35</v>
